--- a/extenbooks/XS1503.xlsx
+++ b/extenbooks/XS1503.xlsx
@@ -447,22 +447,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>XS1503 — Total Unproductive Labor â€” Mohun (Mohun 2013)</t>
+          <t>XS1503 — Total Unproductive Employment Share - Mohun (2014)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE, units=thousands_workers</t>
+          <t>Mohun 2014, RRPE 46(3):355-379, units=share</t>
         </is>
       </c>
     </row>
@@ -480,338 +480,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1948</v>
+        <v>1964</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14095.82930585761</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1949</v>
+        <v>2003</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15502.0884477503</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1950</v>
+        <v>2010</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>16305.56931048863</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>17611.44769566179</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>17989.35730750821</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>18421.60052697869</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1954</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>18819.2306664735</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>19033.20294344155</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1956</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>20051.92452783232</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1957</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>21667.80687710578</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>23173.89181271328</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>24381.47410291775</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>26270.51619965525</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>27052.16767728547</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>27442.58108194811</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>28360.80267488769</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1964</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>28046.23574965509</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>28235.21011526187</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>29258.7961767835</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>31250.10711384425</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>32950.25498113666</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>34959.70688510925</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>36315.29718258603</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1971</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>36870.30686348525</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>38651.42045103699</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>37679.40529413654</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>37743.75680178418</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1975</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>37770.13447132942</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>38923.16578447572</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>39982.52567199793</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>41592.08022486464</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>46011.18367379901</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>46851.56663395891</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>47912.95791848686</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>47677.00935030744</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>48406.70113890422</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>47919.71414001242</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>48036.11219801993</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>49190.7330643012</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>50458.09737244133</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>53955.69737710173</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>55981.31476204339</v>
+        <v>0.475</v>
       </c>
     </row>
   </sheetData>
@@ -825,11 +513,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Total Unproductive Labor â€” Mohun (Mohun 2013)</t>
+          <t>Total Unproductive Employment Share - Mohun (2014)</t>
         </is>
       </c>
     </row>
@@ -896,7 +584,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>thousands_workers</t>
+          <t>share</t>
         </is>
       </c>
     </row>
@@ -920,7 +608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1989</t>
+          <t>1964-2010</t>
         </is>
       </c>
     </row>
@@ -997,7 +685,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE</t>
+          <t>Mohun 2014, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1014,19 +702,23 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t># XS1503 — Total Unproductive Labor (Mohun 2013)</t>
+          <t>&gt; **D4 REBUILD (2026-07-02) — SUPERSEDES the text below (pending D5 doc-regen).**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>&gt; This series has been rebuilt from Mohun's ACTUAL published estimates: total unproductive SHARE of total employment (Mohun 2013 Fig 1, identity anchor): 1964=42.0%, peak 2003=49.0%, 2010=47.5%.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>&gt; Units are now a **share/ratio over 1964-2010** (benchmark anchors, table/text-grade), NOT</t>
         </is>
       </c>
     </row>
@@ -1034,17 +726,73 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>&gt; thousands of FTE over 1948-1989. The old 1948-1989 thousands series was a mislabeled</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>&gt; Attribution: **Mohun (2014), RRPE 46(3):355-379**, DOI 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>&gt; Source: `data/source/external_studies/mohun_2013_published_shares.csv`. See D4 report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t># XS1503 — Total Unproductive Labor (Mohun 2013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1061,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1094,12 +842,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
+          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes total unproductive labor ONLY as SHARES (Figure 1), never as a year-by-year FTE-level table. Verbatim published anchors: total unproductive EMPLOYMENT share 1964 = ~42% of employment, peak 2003 = ~49%, 2010 = 47.5%; total unproductive WAGE share 1964 = 50.7% of all wages, peak 2007 = 65.5%, 2010 = 64.8%. HONESTY NOTE: the shipped XS1503 series (source column Lu_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (ST2) backward decomposition. Its 1964 total-unproductive / total-employment ratio is 44.7% (roughly consistent with Mohun's ~42%), but the series covers 1948-1989, not Mohun's 1964-2010. There is no Mohun 2013 published level anchor; the registry 1948 reference value (14095.8293) is tautological (equals the source CSV = the final output). The one genuinely independent check that holds is the decomposition identity XS1501 + XS1502 = XS1503 (verified to 7e-12 across 1948-1989).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>Mohun 2013, Figure 1 (Shares of Total Employment and Wages), Section 3, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1111,12 +859,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Any laboring activity involved in these "metamorphoses" of capital (M – C and C' – M') adds no new value, and is unproductive. Only the wage-labor involved in the transformation of productive capital into commodity capital is productive.</t>
+          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1128,12 +876,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit.</t>
+          <t>Any laboring activity involved in these "metamorphoses" of capital (M – C and C' – M') adds no new value, and is unproductive. Only the wage-labor involved in the transformation of productive capital into commodity capital is productive.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1145,12 +893,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
+          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1162,12 +910,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
+          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1179,127 +927,148 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hence: The NIPA data for "Private Industries" must be adjusted to exclude "Farms" and "Private households."</t>
+          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Total unproductive labor (Lu) = unproductive working class (Lu_wc) + supervisory labor (Lu_sup). Lu_wc is identified by sector location in the circuit of capital (workers in sectors that transform M→C or C'→M' but who are not supervisors). Lu_sup is identified by subtraction (NIPA total FTEs minus working class FTEs, by sector). Sectors classified as wholly unproductive include: wholesale trade, retail trade (except eating &amp; drinking places), FIRE, most business services, legal services, most professional services. Private households and general government are excluded from the pre-tax analysis to avoid double-counting. Classification by SIC (1964-1997) and NAICS (1998-2010) is tabulated in Tables 2 and 3 of the paper.</t>
+          <t>Hence: The NIPA data for "Private Industries" must be adjusted to exclude "Farms" and "Private households."</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 2.1, Tables 2-3, Appendix; full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Total unproductive labor employment share of total employment: 1964 = ~42%; peak 2003 = ~49%; 2010 = 47.5%. Trend: generally increasing, most markedly in the 1980s. Total unproductive wage share of total wages: 1964 = 50.7%; peak 2007 = 65.5%; 2010 = 64.8%. Comparison with Paitaridis and Tsoulfidis (2012): small differences in levels (from minor classification/computation differences and NIPA revisions); trends are negligible. The unproductive wage share considerably exceeds the employment share and increases at a much faster rate — entirely driven by the supervisory wage component.</t>
+          <t>Total unproductive labor (Lu) = unproductive working class (Lu_wc) + supervisory labor (Lu_sup). Lu_wc is identified by sector location in the circuit of capital (workers in sectors that transform M→C or C'→M' but who are not supervisors). Lu_sup is identified by subtraction (NIPA total FTEs minus working class FTEs, by sector). Sectors classified as wholly unproductive include: wholesale trade, retail trade (except eating &amp; drinking places), FIRE, most business services, legal services, most professional services. Private households and general government are excluded from the pre-tax analysis to avoid double-counting. Classification by SIC (1964-1997) and NAICS (1998-2010) is tabulated in Tables 2 and 3 of the paper.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3, Fig 1; full_transcription.md</t>
+          <t>Mohun_2013, Section 2.1, Tables 2-3, Appendix; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>decomposition</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Total unproductive decomposed into two components with divergent behavior: (1) Working class unproductive (Lu_wc, XS1501): employment share rises modestly (25.1%→30%), wage share of VALUE ADDED flat at 12.8%; (2) Supervisory (Lu_sup, XS1502): employment share flat (16.8-19.9%), wage share of TOTAL WAGES explodes (32%→47.8%). Equation 12: Y = Wp/Y + Wu_wc/Y + Wu_sup/Y + Π/Y. The stability of Wu_wc/Y means working class unproductive labor is NOT a burden; only supervisory wage absorption of value added constitutes a burden in the neoliberal era.</t>
+          <t>Total unproductive labor employment share of total employment: 1964 = ~42%; peak 2003 = ~49%; 2010 = 47.5%. Trend: generally increasing, most markedly in the 1980s. Total unproductive wage share of total wages: 1964 = 50.7%; peak 2007 = 65.5%; 2010 = 64.8%. Comparison with Paitaridis and Tsoulfidis (2012): small differences in levels (from minor classification/computation differences and NIPA revisions); trends are negligible. The unproductive wage share considerably exceeds the employment share and increases at a much faster rate — entirely driven by the supervisory wage component.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mohun_2013, Sections 4-5, Figs 1-4; full_transcription.md</t>
+          <t>Mohun_2013, Section 3, Fig 1; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>causes_of_growth</t>
+          <t>decomposition</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Three factors cited by Paitaridis and Tsoulfidis (2012) for unproductive labor growth: (1) intensification of competition → more sales, administration, supervision resources; (2) expansion of welfare benefits; (3) increased military expenditures. Mohun notes only (1) is relevant in his pre-tax framework. Moseley (1991) disaggregated growth as: ~2/3 commercial labor (slow productivity, person-to-person transactions), ~1/6 financial labor (checking accounts, bank output), ~1/6 supervisory labor (firm size, bureaucratic control, class conflict management). Information technology post-1994 (Moseley 1999) may have slowed unproductive employment growth without reducing wage share.</t>
+          <t>Total unproductive decomposed into two components with divergent behavior: (1) Working class unproductive (Lu_wc, XS1501): employment share rises modestly (25.1%→30%), wage share of VALUE ADDED flat at 12.8%; (2) Supervisory (Lu_sup, XS1502): employment share flat (16.8-19.9%), wage share of TOTAL WAGES explodes (32%→47.8%). Equation 12: Y = Wp/Y + Wu_wc/Y + Wu_sup/Y + Π/Y. The stability of Wu_wc/Y means working class unproductive labor is NOT a burden; only supervisory wage absorption of value added constitutes a burden in the neoliberal era.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3.1; full_transcription.md</t>
+          <t>Mohun_2013, Sections 4-5, Figs 1-4; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>accounting_framework</t>
+          <t>causes_of_growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fundamental accounting equation (Mohun 2013, eq. 1): Y = W + Π = Wp + Wu + Π. Marxian value added (eq. 2): Y = Wp + MSV where MSV = surplus value in money terms. Conservation principle: Y = Hp/λm (aggregate value added = productive hours divided by value of money). This differs from ST (1994) by ~8.41 percentage points in level (Marxian MVA / aggregate VA averages 108.41%, sd 0.83%) but the ratio is approximately constant over 1964-2007, so differences in levels but not trends between the two approaches.</t>
+          <t>Three factors cited by Paitaridis and Tsoulfidis (2012) for unproductive labor growth: (1) intensification of competition → more sales, administration, supervision resources; (2) expansion of welfare benefits; (3) increased military expenditures. Mohun notes only (1) is relevant in his pre-tax framework. Moseley (1991) disaggregated growth as: ~2/3 commercial labor (slow productivity, person-to-person transactions), ~1/6 financial labor (checking accounts, bank output), ~1/6 supervisory labor (firm size, bureaucratic control, class conflict management). Information technology post-1994 (Moseley 1999) may have slowed unproductive employment growth without reducing wage share.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 2.2, Equations 1-3; full_transcription.md</t>
+          <t>Mohun_2013, Section 3.1; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>accounting_framework</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fundamental accounting equation (Mohun 2013, eq. 1): Y = W + Π = Wp + Wu + Π. Marxian value added (eq. 2): Y = Wp + MSV where MSV = surplus value in money terms. Conservation principle: Y = Hp/λm (aggregate value added = productive hours divided by value of money). This differs from ST (1994) by ~8.41 percentage points in level (Marxian MVA / aggregate VA averages 108.41%, sd 0.83%) but the ratio is approximately constant over 1964-2007, so differences in levels but not trends between the two approaches.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 2.2, Equations 1-3; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>construction_note</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Series registry construction: step 1 op=load, subseries=['XS1503-A'], source='Mohun employment CSV'. XS1503 is the directly loaded total unproductive employment series from Mohun's dataset; XS1501 and XS1502 are derived from it by the 81.3%/18.7% class split. Units: thousands of FTEs. Period 1964-2010.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Series registry XS1503</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Total unproductive labor employment (Lu = Lu_wc + Lu_sup), 1964-2010. Employment share rises from ~42% (1964) to ~49% (2003). Wage share rises from 50.7% (1964) to 65.5% (2007). Rise is entirely driven by supervisory wage escalation; working class unproductive VA absorption is flat at 12.8%. Loaded directly from Mohun employment CSV as XS1503-A.</t>
+          <t>D4 rebuild anchors (XS1503): 1964=0.420, 2003=0.490, 2010=0.475 (share of total employment); identity XS1501+XS1502=XS1503 at 1964: 0.251+0.168=0.419 vs 0.420. Source = Mohun 2013 Figure 1 (p.7/361), text-reported benchmark values (table/text-grade). These are the primary validation reference values (external, non-tautological). Non-benchmark annual points are figure-grade and were NOT fabricated.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 1 (p.7/361)</t>
         </is>
       </c>
     </row>
@@ -1307,23 +1076,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total unproductive labor employment (Lu = Lu_wc + Lu_sup), 1964-2010. Employment share rises from ~42% (1964) to ~49% (2003). Wage share rises from 50.7% (1964) to 65.5% (2007). Rise is entirely driven by supervisory wage escalation; working class unproductive VA absorption is flat at 12.8%. Loaded directly from Mohun employment CSV as XS1503-A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Classification of NAICS categories 54 (Professional, scientific and technical) and 56 (Administrative and support) requires judgment for subdivisions; assessed as negligible</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Private households and general government excluded (pre-tax framework); post-tax analysis would require different treatment</t>
         </is>
       </c>
     </row>
@@ -1331,31 +1097,31 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Classification of NAICS categories 54 (Professional, scientific and technical) and 56 (Administrative and support) requires judgment for subdivisions; assessed as negligible</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Private households and general government excluded (pre-tax framework); post-tax analysis would require different treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Comparison with Paitaridis and Tsoulfidis (2012) shows small level differences; trends consistent</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>XS1501</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>XS1502</t>
         </is>
       </c>
     </row>
@@ -1363,49 +1129,65 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>XS1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XS1502</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>XS1504</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Mohun_2013</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Mohun_2013</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mohun_2005</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1468,12 +1250,12 @@
           <t>load</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>XS1503-A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3"/>
@@ -1506,7 +1288,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1948": 14095.8293}</t>
+          <t>{"1964": 0.42, "2003": 0.49, "2010": 0.475}</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1300,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[10000, 150000]</t>
+          <t>[0.38, 0.52]</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1312,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1324,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1503.xlsx
+++ b/extenbooks/XS1503.xlsx
@@ -734,7 +734,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+          <t>&gt; predecessor-build decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_predecessor-build/).</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes total unproductive labor ONLY as SHARES (Figure 1), never as a year-by-year FTE-level table. Verbatim published anchors: total unproductive EMPLOYMENT share 1964 = ~42% of employment, peak 2003 = ~49%, 2010 = 47.5%; total unproductive WAGE share 1964 = 50.7% of all wages, peak 2007 = 65.5%, 2010 = 64.8%. HONESTY NOTE: the shipped XS1503 series (source column Lu_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (ST2) backward decomposition. Its 1964 total-unproductive / total-employment ratio is 44.7% (roughly consistent with Mohun's ~42%), but the series covers 1948-1989, not Mohun's 1964-2010. There is no Mohun 2013 published level anchor; the registry 1948 reference value (14095.8293) is tautological (equals the source CSV = the final output). The one genuinely independent check that holds is the decomposition identity XS1501 + XS1502 = XS1503 (verified to 7e-12 across 1948-1989).</t>
+          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes total unproductive labor ONLY as SHARES (Figure 1), never as a year-by-year FTE-level table. Verbatim published anchors: total unproductive EMPLOYMENT share 1964 = ~42% of employment, peak 2003 = ~49%, 2010 = 47.5%; total unproductive WAGE share 1964 = 50.7% of all wages, peak 2007 = 65.5%, 2010 = 64.8%. HONESTY NOTE: the shipped XS1503 series (source column Lu_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (predecessor-build) backward decomposition. Its 1964 total-unproductive / total-employment ratio is 44.7% (roughly consistent with Mohun's ~42%), but the series covers 1948-1989, not Mohun's 1964-2010. There is no Mohun 2013 published level anchor; the registry 1948 reference value (14095.8293) is tautological (equals the source CSV = the final output). The one genuinely independent check that holds is the decomposition identity XS1501 + XS1502 = XS1503 (verified to 7e-12 across 1948-1989).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
